--- a/investors_test_15.xlsx
+++ b/investors_test_15.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dantez\Documents\ofds\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91FAA03E-28DA-4E14-8453-0BE892A92783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04F8A0F2-2746-4064-98DA-C08E2F2E8D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
   <si>
     <t>investor_name</t>
   </si>
@@ -34,9 +34,6 @@
     <t>amount(usd)</t>
   </si>
   <si>
-    <t>date_transferred</t>
-  </si>
-  <si>
     <t>John Smith</t>
   </si>
   <si>
@@ -67,9 +64,6 @@
     <t>michael.j@example.com</t>
   </si>
   <si>
-    <t>AXIOM-003</t>
-  </si>
-  <si>
     <t>Atium</t>
   </si>
   <si>
@@ -89,6 +83,24 @@
   </si>
   <si>
     <t>fund_name</t>
+  </si>
+  <si>
+    <t>ATIUM-003</t>
+  </si>
+  <si>
+    <t>date_deposited</t>
+  </si>
+  <si>
+    <t>Wealth_manager</t>
+  </si>
+  <si>
+    <t>IFA</t>
+  </si>
+  <si>
+    <t>Contract_note</t>
+  </si>
+  <si>
+    <t>Valuation</t>
   </si>
 </sst>
 </file>
@@ -171,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -190,6 +202,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -492,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -501,9 +514,12 @@
     <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="17.44140625" customWidth="1"/>
     <col min="6" max="6" width="23.5546875" customWidth="1"/>
+    <col min="7" max="7" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -517,187 +533,259 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="D2" s="3">
         <v>5000</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="D3" s="3">
         <v>5000</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D4" s="3">
         <v>5000</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>18</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -708,7 +796,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -719,7 +807,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B22" s="8">
         <v>3</v>
